--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_938_Indonesia_Indian_Ocean.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_938_Indonesia_Indian_Ocean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R9942e2e79fe34774"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R502137d442a14c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb0100ee6a79f4aef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rdf762f2ce5ed4581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd4ad371259c7477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R533f6ee9bb984b9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0562e91b6a9247f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R92427f0c55954b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4ba7c4585e24457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R190f95990b4b4232"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6285d659f9514393"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rde8a648c41244e3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ938CommercialTable" displayName="EEZ938CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ938CommercialTable" displayName="EEZ938CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ938FunctionalTable" displayName="EEZ938FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ938FunctionalTable" displayName="EEZ938FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ938ValidationTable" displayName="EEZ938ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ938ValidationTable" displayName="EEZ938ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10543,7 +10497,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78e8749cde0944fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aad8b9712f14c65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10553,20 +10507,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10574,606 +10518,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>104223.7830808987</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.434908096205375</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>272.21252010396614</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>104223.7830808987</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>272.94197703172307</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$148,A2,'Species'!$U$2:$U$148))</x:f>
-        <x:v>28447045.40782594</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.434908096205375</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>272.21252010396614</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>28371018.647220545</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>76026.76060539484</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0026797332006563</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0026797332006562634</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>161439.37040962788</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.012354216349444</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>102.88551039014398</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>161439.37040962788</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>136.92322135685413</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$148,A3,'Species'!$U$2:$U$148))</x:f>
-        <x:v>22104798.650308646</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.012354216349444</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>102.88551039014398</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>16609772.021658072</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>5495026.628650574</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.3308309482806515</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.3308309482806515</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>10823.8837436874</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.8282868629043634</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>673.4213218701054</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>10823.8837436874</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>675.1371325590711</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$148,A4,'Species'!$U$2:$U$148))</x:f>
-        <x:v>7307605.833865855</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.8282868629043634</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>673.4213218701054</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>7289034.098442314</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>18571.735423540697</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0025479007468918</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0025479007468917625</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>147055.0080622018</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.7917344110961304</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>61.90623772371888</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>147055.0080622018</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>168.8939536423986</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$148,A5,'Species'!$U$2:$U$148))</x:f>
-        <x:v>24836701.714540064</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.7917344110961304</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>61.90623772371888</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>9103622.287562063</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>15733079.426978001</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.72822190222825</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.7282219022282501</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>58545.934609172495</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0156213928486992</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.3662431843586</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>58545.934609172495</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10.40777353534856</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$148,A6,'Species'!$U$2:$U$148))</x:f>
-        <x:v>609332.8288275929</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0156213928486992</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.3662431843586</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>606901.3956142387</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2431.433213354205</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.004006306841482</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.004006306841481846</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>581112.6346794202</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3203126409146733</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>209.08007196765905</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>581112.6346794202</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>222.90256077676884</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$148,A7,'Species'!$U$2:$U$148))</x:f>
-        <x:v>129531494.36977771</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3203126409146733</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>209.08007196765905</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>121499071.48008913</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>8032422.889688581</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.066110981687666</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0661109816876659</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>784201.2109761894</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6450194043121575</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>441.59017719695004</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>784201.2109761894</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>875.6385415750908</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$148,A8,'Species'!$U$2:$U$148))</x:f>
-        <x:v>686676804.6806105</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6450194043121575</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>441.59017719695004</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>346295551.71303827</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>340381252.9675723</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.9829212396283769</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9829212396283769</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>887.9142537995</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>887.9142537995</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$148,A9,'Species'!$U$2:$U$148))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>705295.3618070843</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>705295.3618070843</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>68795.0982269668</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.293927078851093</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1967.5558952661256</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>68795.0982269668</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2000.5865166217152</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$148,A10,'Species'!$U$2:$U$148))</x:f>
-        <x:v>137630545.92253625</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.293927078851093</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1967.5558952661256</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>135358201.08188072</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2272344.8406555355</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0167876406637597</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.016787640663759644</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>195622.7344825464</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.413894471405276</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2593.5490827660724</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>195622.7344825464</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2615.691679980439</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$148,A11,'Species'!$U$2:$U$148))</x:f>
-        <x:v>511688759.0010191</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.413894471405276</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2593.5490827660724</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>507357163.58539915</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4331595.415619969</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0085375662876412</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.008537566287641208</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bfecf1c151b488c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55b8fc14d7034cb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11183,20 +10733,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11204,1092 +10744,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>22629.126029438103</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7055341258111136</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>507.61462459260696</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>22629.126029438103</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>513.3993469373571</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$148,A2,'Species'!$U$2:$U$148))</x:f>
-        <x:v>11617778.52527667</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7055341258111136</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>507.61462459260696</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>11486875.314292014</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>130903.21098465659</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.011395893783385</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.011395893783384792</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>10338.3368432905</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>10338.3368432905</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$148,A3,'Species'!$U$2:$U$148))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2981608.914598427</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>2981608.914598427</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>42284.86686963379</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.359126687370862</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2286.265629118007</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>42284.86686963379</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2341.557313667854</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$148,A4,'Species'!$U$2:$U$148))</x:f>
-        <x:v>99012439.27606255</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.359126687370862</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2286.265629118007</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>96674437.75587447</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2338001.5201880783</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0241842784345132</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.024184278434513144</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>62411.5974254076</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.787456945088495</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>612.9950182840453</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>62411.5974254076</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>924.7613296031701</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$148,A5,'Species'!$U$2:$U$148))</x:f>
-        <x:v>57715831.81777772</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.787456945088495</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>612.9950182840453</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>38257998.304924205</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>19457833.512853518</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.5085951794385721</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.5085951794385722</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>189252.1260156153</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.454417049680887</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2847.1939337157323</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>189252.1260156153</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2859.0491264375614</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$148,A6,'Species'!$U$2:$U$148))</x:f>
-        <x:v>541081125.5613962</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.454417049680887</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2847.1939337157323</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>538837505.1344652</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2243620.4269310236</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0041638163742355</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0041638163742353735</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>207.992458146</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.427624125179274</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>267.6850551288531</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>207.992458146</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>279.7928926666469</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$148,A7,'Species'!$U$2:$U$148))</x:f>
-        <x:v>58194.811517515824</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.427624125179274</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>267.6850551288531</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>55676.472625197675</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2518.3388923181483</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.045231653040793</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.045231653040792956</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>68587.1057688208</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.296554168576101</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1979.4939036730154</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>68587.1057688208</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2005.804874967594</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$148,A8,'Species'!$U$2:$U$148))</x:f>
-        <x:v>137572351.11101875</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.296554168576101</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1979.4939036730154</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>135767757.73995706</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1804593.3710616827</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0132917667721826</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.013291766772182485</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>36144.884041380305</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.40967899059542</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>256.8496572936665</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>36144.884041380305</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>264.00711506528637</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$148,A9,'Species'!$U$2:$U$148))</x:f>
-        <x:v>9542506.560134122</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.40967899059542</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>256.8496572936665</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>9283801.078947846</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>258705.4811862763</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0278663317951655</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.027866331795165518</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>44409.4801169266</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.1192153483787224</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>131.58771586204745</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>44409.4801169266</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>144.50758788271304</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$148,A10,'Species'!$U$2:$U$148))</x:f>
-        <x:v>6417506.850822368</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.1192153483787224</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>131.58771586204745</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5843742.051207383</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>573764.7996149845</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0981844842888708</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09818448428887074</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>500252.07487577276</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.2871239107362813</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>193.69745330311724</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>500252.07487577276</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>200.87232570819165</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$148,A11,'Species'!$U$2:$U$148))</x:f>
-        <x:v>100486797.7206449</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.2871239107362813</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>193.69745330311724</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>96897552.91303751</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>3589244.8076073974</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0370416455287434</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.03704164552874345</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>365714.2282545721</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5856869153662694</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>385.2005649147647</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>365714.2282545721</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>871.7797775746261</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$148,A12,'Species'!$U$2:$U$148))</x:f>
-        <x:v>318822268.5636469</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5856869153662694</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>385.2005649147647</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>140873327.32102835</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>177948941.24261856</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>2.263184057810324</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.263184057810324</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>98499.52598226978</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.6396568650455166</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>436.1710784149781</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>98499.52598226978</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>789.8644216349437</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$148,A13,'Species'!$U$2:$U$148))</x:f>
-        <x:v>77801271.12130164</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.6396568650455166</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>436.1710784149781</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>42962644.47105077</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>34838626.65025087</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.8109050799637332</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.8109050799637333</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>59724.69629048479</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.0213192541839646</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>10.50314241357033</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>59724.69629048479</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>10.600719455684265</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$148,A14,'Species'!$U$2:$U$148))</x:f>
-        <x:v>633124.749951376</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.0213192541839646</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>10.50314241357033</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>627296.9907461974</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5827.7592051785905</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0092902712609002</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.009290271260900223</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>125294.48636824758</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.8977341855072263</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>79.01948329235042</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>125294.48636824758</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>100.26213007692316</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$148,A15,'Species'!$U$2:$U$148))</x:f>
-        <x:v>12562292.090174515</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.8977341855072263</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>79.01948329235042</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>9900705.572199367</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>2661586.517975148</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.268827963680562</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.26882796368056183</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>68278.04071842258</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.2233247575652215</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>167.234069300788</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>68278.04071842258</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>167.69726509001043</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$148,A16,'Species'!$U$2:$U$148))</x:f>
-        <x:v>11450040.694183838</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.2233247575652215</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>167.234069300788</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>11418414.593226707</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>31626.100957131013</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0027697453704205</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.002769745370420453</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>25402.7041698791</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.810373712494351</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>646.2100567217659</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>25402.7041698791</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>682.0474046826847</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$148,A17,'Species'!$U$2:$U$148))</x:f>
-        <x:v>17325848.450988054</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.810373712494351</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>646.2100567217659</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>16415482.902503813</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>910365.5484842416</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0554577379106762</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.05545773791067613</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>341298.8358254742</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.2526345944484767</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>178.90999124021212</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>341298.8358254742</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>308.79939037274534</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$148,A18,'Species'!$U$2:$U$148))</x:f>
-        <x:v>105392872.43783411</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.2526345944484767</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>178.90999124021212</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>61061771.72783018</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>44331100.710003935</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.7260041668558253</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.7260041668558253</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>41153.5807270413</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.8285314382309243</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>673.8006695978975</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>41153.5807270413</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>771.6684215294995</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$148,A19,'Species'!$U$2:$U$148))</x:f>
-        <x:v>31756918.67992279</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.8285314382309243</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>673.8006695978975</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>27729310.250231557</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>4027608.4296912327</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1452473355213586</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.14524733552135866</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>10823.8837436874</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.8282868629043634</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>673.4213218701054</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>10823.8837436874</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>675.1371325590711</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$148,A20,'Species'!$U$2:$U$148))</x:f>
-        <x:v>7307605.833865855</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.8282868629043634</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>673.4213218701054</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>7289034.098442314</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>18571.735423540697</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0025479007468918</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.0025479007468917625</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89fed80f1bf945bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R879f50055bde4489"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12464,7 +11295,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12563,7 +11394,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1549538383.7711184</x:v>
+        <x:v>1173195631.6727116</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12577,7 +11408,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1549538383.7711182</x:v>
+        <x:v>1254364943.6071885</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12591,7 +11422,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.384185791015625e-7</x:v>
+        <x:v>-376342752.09840655</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12605,7 +11436,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-295173440.1639297</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12616,9 +11447,9 @@
         <x:v>EEZ_938</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12630,47 +11461,19 @@
         <x:v>EEZ_938</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_938</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_938</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f94c743ab8643e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34ebc2bc5f349f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12717,7 +11520,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
